--- a/R_analysis/output/tables/Tabela_Sensibilidade_Temporal.xlsx
+++ b/R_analysis/output/tables/Tabela_Sensibilidade_Temporal.xlsx
@@ -404,7 +404,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -431,7 +431,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -458,7 +458,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -485,7 +485,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -512,7 +512,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -566,7 +566,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -620,7 +620,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -674,7 +674,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -701,7 +701,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -728,7 +728,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brasil — Gestacional</t>
+          <t>Brasil — Gestational</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -782,7 +782,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -809,7 +809,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -836,7 +836,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -863,7 +863,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -917,7 +917,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -944,7 +944,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -998,7 +998,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1052,7 +1052,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brasil — Congênita</t>
+          <t>Brasil — Congenital</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
